--- a/data/bsc_stats.xlsx
+++ b/data/bsc_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B823C763-8234-7747-B427-B663A446C188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB71AC4-C307-6D44-8337-38ADA414FD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19260" yWindow="1880" windowWidth="18900" windowHeight="16740" xr2:uid="{9AB36089-2A1E-A444-9F4E-CE79D745AFAD}"/>
   </bookViews>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0586C9AE-BA6B-444C-810B-D9BD6C3F18D2}">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1216,6 +1216,102 @@
         <v>40</v>
       </c>
     </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>57</v>
+      </c>
+      <c r="B109">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>81</v>
+      </c>
+      <c r="B110">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>53</v>
+      </c>
+      <c r="B111">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>76</v>
+      </c>
+      <c r="B112">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>71</v>
+      </c>
+      <c r="B113">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>78</v>
+      </c>
+      <c r="B114">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>46</v>
+      </c>
+      <c r="B115">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>94</v>
+      </c>
+      <c r="B116">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>61</v>
+      </c>
+      <c r="B117">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>42</v>
+      </c>
+      <c r="B118">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>61</v>
+      </c>
+      <c r="B119">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>52</v>
+      </c>
+      <c r="B120">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/bsc_stats.xlsx
+++ b/data/bsc_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/jkruppa.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB71AC4-C307-6D44-8337-38ADA414FD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A596367-6B7F-B140-8D88-D8A30C54D27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19260" yWindow="1880" windowWidth="18900" windowHeight="16740" xr2:uid="{9AB36089-2A1E-A444-9F4E-CE79D745AFAD}"/>
   </bookViews>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0586C9AE-BA6B-444C-810B-D9BD6C3F18D2}">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1312,6 +1312,270 @@
         <v>36</v>
       </c>
     </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>66</v>
+      </c>
+      <c r="B121">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>87</v>
+      </c>
+      <c r="B122">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>76</v>
+      </c>
+      <c r="B123">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>57</v>
+      </c>
+      <c r="B124">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>40</v>
+      </c>
+      <c r="B125">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>53</v>
+      </c>
+      <c r="B126">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>76</v>
+      </c>
+      <c r="B127">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>104</v>
+      </c>
+      <c r="B128">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>78</v>
+      </c>
+      <c r="B129">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>78</v>
+      </c>
+      <c r="B130">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>79</v>
+      </c>
+      <c r="B131">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>64</v>
+      </c>
+      <c r="B132">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>65</v>
+      </c>
+      <c r="B133">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>57</v>
+      </c>
+      <c r="B134">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>90</v>
+      </c>
+      <c r="B135">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>46</v>
+      </c>
+      <c r="B136">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>76</v>
+      </c>
+      <c r="B137">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>80</v>
+      </c>
+      <c r="B138">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>58</v>
+      </c>
+      <c r="B139">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>78</v>
+      </c>
+      <c r="B140">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>63</v>
+      </c>
+      <c r="B141">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>70</v>
+      </c>
+      <c r="B142">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>66</v>
+      </c>
+      <c r="B143">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>44</v>
+      </c>
+      <c r="B144">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>69</v>
+      </c>
+      <c r="B145">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>69</v>
+      </c>
+      <c r="B146">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>79</v>
+      </c>
+      <c r="B147">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>48</v>
+      </c>
+      <c r="B148">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>49</v>
+      </c>
+      <c r="B149">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>58</v>
+      </c>
+      <c r="B150">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>58</v>
+      </c>
+      <c r="B151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>76</v>
+      </c>
+      <c r="B152">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>58</v>
+      </c>
+      <c r="B153">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
